--- a/artfynd/A 23592-2025 artfynd.xlsx
+++ b/artfynd/A 23592-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126421053</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>556447</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6972112</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23592-2025 artfynd.xlsx
+++ b/artfynd/A 23592-2025 artfynd.xlsx
@@ -1017,7 +1017,7 @@
         <v>126421053</v>
       </c>
       <c r="B5" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23592-2025 artfynd.xlsx
+++ b/artfynd/A 23592-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104451243</v>
+        <v>104451244</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556533.9798999598</v>
+        <v>556534</v>
       </c>
       <c r="R2" t="n">
-        <v>6972088.148217855</v>
+        <v>6972088</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104451216</v>
+        <v>81142532</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +794,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556434.7419623266</v>
+        <v>556553</v>
       </c>
       <c r="R3" t="n">
-        <v>6972117.929047345</v>
+        <v>6972023</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,66 +868,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104451244</v>
+        <v>81142533</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräcke, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556533.9798999598</v>
+        <v>556584</v>
       </c>
       <c r="R4" t="n">
-        <v>6972088.148217855</v>
+        <v>6972027</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,22 +965,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Mattias Lif</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126421053</v>
+        <v>81142545</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,34 +988,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brantbergtjärnen, Jmt</t>
+          <t>Storåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556447</v>
+        <v>556387</v>
       </c>
       <c r="R5" t="n">
-        <v>6972112</v>
+        <v>6972211</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2019-10-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,19 +1058,656 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Senvuxna myrgranar</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81142530</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>556595</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6972040</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark av gammal, senvuxen gran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>81142496</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556618</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104451243</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556534</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104451216</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bräcke, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556435</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972117</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126421053</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556447</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972112</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81142535</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556507</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971990</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-10-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23592-2025 artfynd.xlsx
+++ b/artfynd/A 23592-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142533</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142545</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142530</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142496</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451243</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104451216</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126421053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,8 +1758,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81142535</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>